--- a/data/trans_dic/P23_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,5; 36,27</t>
+          <t>27,92; 36,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,95; 38,7</t>
+          <t>29,2; 39,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 29,77</t>
+          <t>21,21; 29,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,26; 35,15</t>
+          <t>25,2; 35,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,4; 37,44</t>
+          <t>26,11; 37,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,9</t>
+          <t>15,51; 23,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,17; 34,9</t>
+          <t>27,9; 34,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,84</t>
+          <t>29,12; 36,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 26,17</t>
+          <t>19,51; 25,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 41,96</t>
+          <t>31,94; 42,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,29; 41,59</t>
+          <t>31,26; 40,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,14</t>
+          <t>23,88; 33,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,9; 40,78</t>
+          <t>31,02; 41,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,96; 43,2</t>
+          <t>31,84; 42,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 32,14</t>
+          <t>22,2; 31,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,68; 39,9</t>
+          <t>32,19; 39,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,74; 40,58</t>
+          <t>32,97; 40,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 31,11</t>
+          <t>24,38; 31,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,56; 51,4</t>
+          <t>42,74; 51,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,42; 47,33</t>
+          <t>39,49; 47,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,07; 46,23</t>
+          <t>37,28; 46,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 34,79</t>
+          <t>21,26; 35,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,88; 38,97</t>
+          <t>27,06; 38,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,93; 39,29</t>
+          <t>24,41; 39,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,65; 46,27</t>
+          <t>39,03; 46,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 43,68</t>
+          <t>36,66; 43,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,41; 42,84</t>
+          <t>35,43; 43,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,48; 48,25</t>
+          <t>42,82; 48,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 46,04</t>
+          <t>39,74; 45,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,26; 40,77</t>
+          <t>34,97; 41,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,95</t>
+          <t>30,0; 37,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,67; 41,09</t>
+          <t>33,57; 40,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,96; 41,59</t>
+          <t>35,0; 41,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,07; 43,28</t>
+          <t>38,97; 43,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,23; 43,07</t>
+          <t>38,45; 43,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 40,28</t>
+          <t>36,03; 40,38</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,67; 58,72</t>
+          <t>48,44; 58,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,25; 47,18</t>
+          <t>38,35; 47,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,45; 43,17</t>
+          <t>35,24; 43,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,12; 36,0</t>
+          <t>27,99; 35,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 31,77</t>
+          <t>25,28; 31,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 33,11</t>
+          <t>26,06; 32,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,67; 43,54</t>
+          <t>36,43; 43,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,51; 36,8</t>
+          <t>31,53; 37,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,46; 36,54</t>
+          <t>31,43; 36,44</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,65; 34,96</t>
+          <t>24,81; 35,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,96; 29,37</t>
+          <t>19,18; 29,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,01; 31,54</t>
+          <t>20,46; 31,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,57</t>
+          <t>11,82; 15,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 16,88</t>
+          <t>12,77; 17,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 18,55</t>
+          <t>13,61; 18,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,83; 18,44</t>
+          <t>14,94; 18,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,66; 18,55</t>
+          <t>14,68; 18,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 20,17</t>
+          <t>15,96; 20,32</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,56; 44,05</t>
+          <t>40,54; 43,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,84; 41,38</t>
+          <t>37,91; 41,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,54; 36,74</t>
+          <t>33,36; 36,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,15; 27,12</t>
+          <t>23,93; 26,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,95; 29,13</t>
+          <t>25,87; 29,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,86; 27,89</t>
+          <t>24,61; 27,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,65; 34,98</t>
+          <t>32,6; 35,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,27; 34,62</t>
+          <t>32,36; 34,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,26; 31,7</t>
+          <t>29,37; 31,63</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>130306; 171823</t>
+          <t>132268; 172301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>126561; 169180</t>
+          <t>127651; 170909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90630; 127762</t>
+          <t>90994; 128658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77480; 107809</t>
+          <t>77273; 109460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83010; 117719</t>
+          <t>82105; 116990</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52481; 82960</t>
+          <t>53839; 82368</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>219863; 272366</t>
+          <t>217758; 269777</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>221043; 276905</t>
+          <t>218912; 273430</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153156; 203112</t>
+          <t>151449; 199183</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>116435; 153948</t>
+          <t>117186; 154573</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131038; 174169</t>
+          <t>130915; 171150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89656; 124658</t>
+          <t>89835; 125591</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114916; 151665</t>
+          <t>115334; 153039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108029; 146009</t>
+          <t>107609; 145238</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83402; 119324</t>
+          <t>82401; 118369</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>241458; 294779</t>
+          <t>237832; 293919</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>247796; 307115</t>
+          <t>249505; 306851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180838; 232537</t>
+          <t>182241; 231757</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>230814; 278778</t>
+          <t>231842; 276686</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>248117; 297885</t>
+          <t>248544; 300793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>193497; 241300</t>
+          <t>194585; 240601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36456; 58372</t>
+          <t>35673; 59070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69933; 101367</t>
+          <t>70379; 100165</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41407; 65269</t>
+          <t>40545; 66328</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>274487; 328587</t>
+          <t>277163; 327132</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>328061; 388525</t>
+          <t>326080; 387145</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243660; 294742</t>
+          <t>243796; 297949</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>526056; 597482</t>
+          <t>530297; 599929</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>465106; 533168</t>
+          <t>460199; 529579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>405101; 468402</t>
+          <t>401767; 472498</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>216307; 263940</t>
+          <t>214318; 265817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>257795; 314648</t>
+          <t>257062; 313797</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>288381; 343131</t>
+          <t>288694; 344372</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>762889; 845078</t>
+          <t>760972; 848164</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>735422; 828576</t>
+          <t>739610; 830952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711253; 794935</t>
+          <t>711055; 797043</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>167109; 205829</t>
+          <t>169808; 205795</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>195300; 240875</t>
+          <t>195820; 241573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220029; 267940</t>
+          <t>218733; 268243</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159938; 204729</t>
+          <t>159204; 204183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>189483; 241649</t>
+          <t>192276; 243272</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>193723; 244103</t>
+          <t>192089; 242825</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>337105; 400243</t>
+          <t>334898; 399874</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>400481; 467740</t>
+          <t>400750; 471736</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>427155; 496108</t>
+          <t>426787; 494790</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73261; 103884</t>
+          <t>73717; 104418</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50607; 78375</t>
+          <t>51195; 77701</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60339; 90578</t>
+          <t>58745; 89408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>145347; 194445</t>
+          <t>147583; 196095</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>141592; 187310</t>
+          <t>141639; 188574</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>151222; 200287</t>
+          <t>146901; 201066</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>229320; 285069</t>
+          <t>230973; 288110</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>201820; 255234</t>
+          <t>202037; 256299</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>218778; 275611</t>
+          <t>218135; 277796</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1326109; 1440110</t>
+          <t>1325402; 1436148</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1294421; 1415449</t>
+          <t>1296737; 1415226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1134909; 1243258</t>
+          <t>1128865; 1248850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>815977; 915986</t>
+          <t>808288; 909190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>920672; 1033500</t>
+          <t>918013; 1033139</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>876658; 983412</t>
+          <t>867898; 975105</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2170200; 2325416</t>
+          <t>2166893; 2328175</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2249069; 2412621</t>
+          <t>2255438; 2418628</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2021714; 2190228</t>
+          <t>2029531; 2185934</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,92; 36,37</t>
+          <t>28,18; 36,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,2; 39,09</t>
+          <t>29,28; 38,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 29,98</t>
+          <t>21,25; 29,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,69</t>
+          <t>25,24; 35,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,11; 37,2</t>
+          <t>26,01; 37,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 23,73</t>
+          <t>15,43; 24,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 34,57</t>
+          <t>27,97; 34,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,12; 36,38</t>
+          <t>29,1; 36,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,51; 25,66</t>
+          <t>19,61; 25,92</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,94; 42,13</t>
+          <t>32,15; 41,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,26; 40,87</t>
+          <t>30,72; 41,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,88; 33,39</t>
+          <t>23,5; 33,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,02; 41,15</t>
+          <t>31,01; 40,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,84; 42,97</t>
+          <t>31,72; 42,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,2; 31,88</t>
+          <t>22,93; 31,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,19; 39,78</t>
+          <t>32,64; 39,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,97; 40,55</t>
+          <t>32,7; 40,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,38; 31,01</t>
+          <t>24,44; 31,2</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,74; 51,01</t>
+          <t>42,67; 51,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 47,79</t>
+          <t>39,28; 47,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 46,1</t>
+          <t>37,39; 46,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,26; 35,21</t>
+          <t>20,66; 33,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,06; 38,51</t>
+          <t>27,26; 38,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,41; 39,93</t>
+          <t>24,79; 39,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,03; 46,06</t>
+          <t>38,86; 46,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,66; 43,52</t>
+          <t>36,88; 43,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 43,3</t>
+          <t>35,29; 42,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,82; 48,45</t>
+          <t>42,7; 48,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,74; 45,73</t>
+          <t>40,13; 46,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,97; 41,13</t>
+          <t>35,26; 41,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,0; 37,21</t>
+          <t>30,77; 37,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,57; 40,98</t>
+          <t>33,81; 41,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,0; 41,74</t>
+          <t>35,05; 41,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,97; 43,44</t>
+          <t>38,86; 43,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,45; 43,2</t>
+          <t>38,22; 43,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,03; 40,38</t>
+          <t>36,04; 40,29</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,44; 58,71</t>
+          <t>48,4; 59,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,35; 47,31</t>
+          <t>38,45; 47,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,24; 43,22</t>
+          <t>35,55; 43,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 35,9</t>
+          <t>27,68; 35,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,28; 31,99</t>
+          <t>24,85; 32,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,06; 32,94</t>
+          <t>26,49; 33,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,43; 43,5</t>
+          <t>36,76; 43,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,53; 37,11</t>
+          <t>31,51; 36,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,43; 36,44</t>
+          <t>31,3; 36,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,81; 35,14</t>
+          <t>24,56; 34,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,11</t>
+          <t>18,82; 29,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,46; 31,14</t>
+          <t>20,24; 30,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 15,7</t>
+          <t>11,79; 15,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,0</t>
+          <t>12,61; 16,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,61; 18,62</t>
+          <t>13,95; 18,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 18,64</t>
+          <t>14,84; 18,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,68; 18,62</t>
+          <t>14,62; 18,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 20,32</t>
+          <t>16,04; 20,18</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,54; 43,93</t>
+          <t>40,67; 44,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,91; 41,37</t>
+          <t>37,91; 41,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,36; 36,91</t>
+          <t>33,26; 36,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,93; 26,91</t>
+          <t>24,01; 26,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 29,12</t>
+          <t>26,01; 29,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,61; 27,65</t>
+          <t>24,78; 27,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,6; 35,02</t>
+          <t>32,6; 34,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,36; 34,71</t>
+          <t>32,27; 34,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,37; 31,63</t>
+          <t>29,5; 31,75</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>132268; 172301</t>
+          <t>133517; 173320</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127651; 170909</t>
+          <t>128032; 169187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90994; 128658</t>
+          <t>91170; 128289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77273; 109460</t>
+          <t>77397; 109002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82105; 116990</t>
+          <t>81774; 116931</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53839; 82368</t>
+          <t>53546; 83710</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>217758; 269777</t>
+          <t>218270; 269560</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>218912; 273430</t>
+          <t>218754; 274258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>151449; 199183</t>
+          <t>152174; 201149</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117186; 154573</t>
+          <t>117959; 153949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130915; 171150</t>
+          <t>128634; 172067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89835; 125591</t>
+          <t>88380; 126387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115334; 153039</t>
+          <t>115299; 152157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>107609; 145238</t>
+          <t>107213; 144703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82401; 118369</t>
+          <t>85114; 118682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>237832; 293919</t>
+          <t>241180; 294924</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>249505; 306851</t>
+          <t>247459; 305074</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182241; 231757</t>
+          <t>182699; 233189</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>231842; 276686</t>
+          <t>231446; 278602</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>248544; 300793</t>
+          <t>247217; 298124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194585; 240601</t>
+          <t>195167; 240983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35673; 59070</t>
+          <t>34658; 57036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70379; 100165</t>
+          <t>70904; 100584</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40545; 66328</t>
+          <t>41179; 65103</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>277163; 327132</t>
+          <t>275964; 330241</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>326080; 387145</t>
+          <t>328061; 384303</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243796; 297949</t>
+          <t>242817; 295807</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>530297; 599929</t>
+          <t>528771; 598253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>460199; 529579</t>
+          <t>464671; 533770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>401767; 472498</t>
+          <t>405052; 471443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>214318; 265817</t>
+          <t>219801; 268791</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>257062; 313797</t>
+          <t>258896; 315083</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>288694; 344372</t>
+          <t>289140; 343617</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>760972; 848164</t>
+          <t>758777; 849334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>739610; 830952</t>
+          <t>735263; 829099</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711055; 797043</t>
+          <t>711392; 795160</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>169808; 205795</t>
+          <t>169681; 206815</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>195820; 241573</t>
+          <t>196333; 241307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>218733; 268243</t>
+          <t>220640; 267811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159204; 204183</t>
+          <t>157432; 204324</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>192276; 243272</t>
+          <t>188973; 243882</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>192089; 242825</t>
+          <t>195244; 245294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>334898; 399874</t>
+          <t>337980; 398721</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>400750; 471736</t>
+          <t>400537; 468434</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>426787; 494790</t>
+          <t>424969; 494460</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73717; 104418</t>
+          <t>72990; 103067</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51195; 77701</t>
+          <t>50217; 78623</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58745; 89408</t>
+          <t>58127; 87939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>147583; 196095</t>
+          <t>147269; 193175</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>141639; 188574</t>
+          <t>139909; 188046</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>146901; 201066</t>
+          <t>150563; 196675</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>230973; 288110</t>
+          <t>229481; 289750</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>202037; 256299</t>
+          <t>201169; 255931</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>218135; 277796</t>
+          <t>219162; 275748</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1325402; 1436148</t>
+          <t>1329459; 1441411</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1296737; 1415226</t>
+          <t>1296920; 1414325</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1128865; 1248850</t>
+          <t>1125355; 1237636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>808288; 909190</t>
+          <t>811096; 908837</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>918013; 1033139</t>
+          <t>922732; 1033789</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>867898; 975105</t>
+          <t>873874; 980028</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2166893; 2328175</t>
+          <t>2167279; 2317612</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2255438; 2418628</t>
+          <t>2249195; 2415869</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2029531; 2185934</t>
+          <t>2038314; 2194178</t>
         </is>
       </c>
     </row>
